--- a/docs/KVD_Windpark_Snag_Checklist.xlsx
+++ b/docs/KVD_Windpark_Snag_Checklist.xlsx
@@ -34,7 +34,7 @@
     <t xml:space="preserve">KVD Windpark: flat snagging checklist</t>
   </si>
   <si>
-    <t xml:space="preserve">RCC framed towers, plaster and paint, aluminium / uPVC windows, wooden internal doors. 5 towers x 24 floors, 2BHK and 3BHK.</t>
+    <t xml:space="preserve">RCC framed towers, plaster and paint, aluminium / uPVC windows, wooden internal doors. Phase 1: towers T1, T2, T3, T6, T7 (T4, T5 are Phase 2). 24 floors, 2BHK and 3BHK.</t>
   </si>
   <si>
     <t xml:space="preserve">Checklist</t>
